--- a/DATA/A077970_valuation.xlsx
+++ b/DATA/A077970_valuation.xlsx
@@ -396,40 +396,40 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>201396855.87683</v>
+        <v>202028093.1019482</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>195927643.631627</v>
+        <v>196247202.7074325</v>
       </c>
       <c r="B3">
         <v>1.667440345024995</v>
       </c>
       <c r="C3">
-        <v>326697657.6970544</v>
+        <v>327230503.3926713</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>241644218.7519742</v>
+        <v>242927204.2853888</v>
       </c>
       <c r="B4">
         <v>1.475303425365941</v>
       </c>
       <c r="C4">
-        <v>356498543.6446643</v>
+        <v>358391336.5968058</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>160399805.16868</v>
+        <v>161371285.3192832</v>
       </c>
       <c r="B5">
         <v>1.822608237072944</v>
       </c>
       <c r="C5">
-        <v>292346006.1253315</v>
+        <v>294116633.8499739</v>
       </c>
     </row>
     <row r="6" spans="1:3">
